--- a/dados/Make_Monetaria_HIPOTETICO.xlsx
+++ b/dados/Make_Monetaria_HIPOTETICO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/768ce10d4f3360c7/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\dev_2026\gd_impacta_mg\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{D92E72CE-7529-4F95-AA15-1F7559977747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D83AF47-B2BC-461B-BD39-F2EF13B67649}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9889FEE-591A-4959-BBA3-FAA6F33B7CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{BD14A59D-08AE-458F-8E9E-A36A88EBC844}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="5" xr2:uid="{BD14A59D-08AE-458F-8E9E-A36A88EBC844}"/>
   </bookViews>
   <sheets>
     <sheet name="Agropec" sheetId="6" r:id="rId1"/>
@@ -24,6 +24,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -295,9 +306,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -335,7 +346,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -441,7 +452,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -583,7 +594,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -591,14 +602,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D994BB5-0A33-4589-9A5B-A2E1612255D1}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -609,7 +620,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -623,7 +634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -641,7 +652,7 @@
         <v>-18.739440999999943</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -659,7 +670,7 @@
         <v>13.122924999999896</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -677,7 +688,7 @@
         <v>8.9787290000000439</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -695,7 +706,7 @@
         <v>-4.2680359999999951</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -713,7 +724,7 @@
         <v>4.5598150000000146</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -731,7 +742,7 @@
         <v>-33.752198000000135</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -749,7 +760,7 @@
         <v>-6.3654169999999795</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -767,7 +778,7 @@
         <v>-54.568358999999873</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -785,7 +796,7 @@
         <v>7.6526950000000227</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -803,7 +814,7 @@
         <v>20.634339000000068</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -821,7 +832,7 @@
         <v>-1.372618999999986</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -839,7 +850,7 @@
         <v>2.8157959999999775</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -857,7 +868,7 @@
         <v>16.845337000000086</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -875,7 +886,7 @@
         <v>3.5288080000000264</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -893,7 +904,7 @@
         <v>-5.7065119999999752</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -911,7 +922,7 @@
         <v>8.4522709999999961</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -929,7 +940,7 @@
         <v>10.444274999999948</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -947,7 +958,7 @@
         <v>4.976348999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -965,7 +976,7 @@
         <v>33.540100000000052</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -983,7 +994,7 @@
         <v>11.203856999999971</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1001,7 +1012,7 @@
         <v>-62.02172900000005</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1019,7 +1030,7 @@
         <v>6.4243160000000898</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -1037,7 +1048,7 @@
         <v>-0.19898200000000088</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -1055,7 +1066,7 @@
         <v>-1.5546570000000202</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -1073,7 +1084,7 @@
         <v>2.907195999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -1091,7 +1102,7 @@
         <v>-8.0051879999999755</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1109,7 +1120,7 @@
         <v>7.2729800000000182</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1127,7 +1138,7 @@
         <v>-2.294860999999969</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1145,7 +1156,7 @@
         <v>-13.044433000000026</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -1163,7 +1174,7 @@
         <v>15.320312000000058</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -1181,7 +1192,7 @@
         <v>28.70184299999994</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1199,7 +1210,7 @@
         <v>-1.4879760000000033</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -1217,7 +1228,7 @@
         <v>-2.8707890000000589</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -1235,7 +1246,7 @@
         <v>-1.4951169999999365</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -1253,7 +1264,7 @@
         <v>6.5894010000000094</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -1271,7 +1282,7 @@
         <v>8.919006999999965</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1289,7 +1300,7 @@
         <v>20.623841000000084</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -1307,7 +1318,7 @@
         <v>-13.530577999999991</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -1325,7 +1336,7 @@
         <v>12.246827000000053</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -1343,7 +1354,7 @@
         <v>-10.111725000000035</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -1361,7 +1372,7 @@
         <v>-4.591186000000107</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -1379,7 +1390,7 @@
         <v>9.1596679999997832</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -1397,7 +1408,7 @@
         <v>16.957276000000093</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -1415,7 +1426,7 @@
         <v>-9.5727539999998044</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -1433,7 +1444,7 @@
         <v>-11.532227000000148</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -1451,7 +1462,7 @@
         <v>6.4783019999999851</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -1469,7 +1480,7 @@
         <v>4.0982589999999988</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -1487,7 +1498,7 @@
         <v>12.765990999999985</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -1505,7 +1516,7 @@
         <v>-15.407531999999946</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -1523,7 +1534,7 @@
         <v>-16.519408999999996</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -1541,7 +1552,7 @@
         <v>-9.9732669999998507</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -1559,7 +1570,7 @@
         <v>-1.4166870000000245</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -1577,7 +1588,7 @@
         <v>4.8604429999999752</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1595,7 +1606,7 @@
         <v>-4.7219239999999445</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1613,7 +1624,7 @@
         <v>10.091003999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -1631,7 +1642,7 @@
         <v>12.79229799999996</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -1649,7 +1660,7 @@
         <v>-2.4379890000000159</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -1667,7 +1678,7 @@
         <v>27.196654999999964</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -1685,7 +1696,7 @@
         <v>21.048583999999892</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -1703,7 +1714,7 @@
         <v>8.0071410000000469</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -1721,7 +1732,7 @@
         <v>10.738831000000005</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -1739,7 +1750,7 @@
         <v>28.588746000000128</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -1757,7 +1768,7 @@
         <v>-116.4990229999994</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -1775,7 +1786,7 @@
         <v>-50.271972999999889</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -1793,7 +1804,7 @@
         <v>27.184570000000122</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -1807,8 +1818,26 @@
         <v>918.879456</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G69" si="1">E68-B68</f>
+        <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>14.084167999999977</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>75381.025983999993</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>75366.506351000018</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>-14.519632999998848</v>
+      </c>
+      <c r="H70">
+        <f>G70/B70</f>
+        <v>-1.9261654787082247E-4</v>
       </c>
     </row>
   </sheetData>
@@ -1818,14 +1847,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{100931DE-165D-40DC-ADFB-F4ABF15FE41E}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -1836,7 +1865,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1850,7 +1879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1868,7 +1897,7 @@
         <v>0.73429900000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1886,7 +1915,7 @@
         <v>2.6893469999999979</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1904,7 +1933,7 @@
         <v>0.32005099999999942</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1922,7 +1951,7 @@
         <v>5.1752999999999716E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1940,7 +1969,7 @@
         <v>0.35699599999999965</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1958,7 +1987,7 @@
         <v>10.138336999999979</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1976,7 +2005,7 @@
         <v>1.2734609999999975</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1994,7 +2023,7 @@
         <v>291.39257800000087</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2012,7 +2041,7 @@
         <v>0.61419300000000021</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2030,7 +2059,7 @@
         <v>1.4240690000000029</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2048,7 +2077,7 @@
         <v>0.51834699999999856</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2066,7 +2095,7 @@
         <v>0.54386099999999971</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2084,7 +2113,7 @@
         <v>0.53546599999999955</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2102,7 +2131,7 @@
         <v>3.5412830000000071</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2120,7 +2149,7 @@
         <v>3.3213049999999953</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2138,7 +2167,7 @@
         <v>30.474731999999904</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2156,7 +2185,7 @@
         <v>0.41640799999999878</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2174,7 +2203,7 @@
         <v>0.33366700000000016</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2192,7 +2221,7 @@
         <v>18.454651000000013</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2210,7 +2239,7 @@
         <v>1.5425270000000069</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2228,7 +2257,7 @@
         <v>0.41813700000000154</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -2246,7 +2275,7 @@
         <v>1.9416249999999948</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2264,7 +2293,7 @@
         <v>0.24701800000000063</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2282,7 +2311,7 @@
         <v>0.45116900000000015</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2300,7 +2329,7 @@
         <v>26.376342999999906</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -2318,7 +2347,7 @@
         <v>37.550416000000041</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -2336,7 +2365,7 @@
         <v>7.4272770000000037</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2354,7 +2383,7 @@
         <v>1.6758430000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -2372,7 +2401,7 @@
         <v>1.3865099999999941</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -2390,7 +2419,7 @@
         <v>5.0437319999999985</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -2408,7 +2437,7 @@
         <v>0.60508699999999926</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -2426,7 +2455,7 @@
         <v>6.8815930000000094</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -2444,7 +2473,7 @@
         <v>0.8438419999999951</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -2462,7 +2491,7 @@
         <v>3.5037700000000029</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -2480,7 +2509,7 @@
         <v>9.2654000000000014E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -2498,7 +2527,7 @@
         <v>2.00498300000001</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -2516,7 +2545,7 @@
         <v>4.0740360000000067</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -2534,7 +2563,7 @@
         <v>0.41358899999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -2552,7 +2581,7 @@
         <v>1.5296869999999956</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -2570,7 +2599,7 @@
         <v>38.820556999999781</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -2588,7 +2617,7 @@
         <v>1.5176400000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -2606,7 +2635,7 @@
         <v>10.08435099999997</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -2624,7 +2653,7 @@
         <v>3.5804369999999892</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -2642,7 +2671,7 @@
         <v>1.1053050000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -2660,7 +2689,7 @@
         <v>1.3256230000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -2678,7 +2707,7 @@
         <v>7.6853999999999978E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -2696,7 +2725,7 @@
         <v>0.28288899999999995</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -2714,7 +2743,7 @@
         <v>1.4091409999999982</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -2732,7 +2761,7 @@
         <v>0.17207799999999907</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -2750,7 +2779,7 @@
         <v>7.1031810000000064</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -2768,7 +2797,7 @@
         <v>0.75553199999999876</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -2786,7 +2815,7 @@
         <v>5.1416480000000035</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -2804,7 +2833,7 @@
         <v>1.0646850000000008</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -2822,7 +2851,7 @@
         <v>0.96134999999999593</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -2840,7 +2869,7 @@
         <v>4.7318810000000013</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -2858,7 +2887,7 @@
         <v>0.72177200000000141</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -2876,7 +2905,7 @@
         <v>3.6519169999999974</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -2894,7 +2923,7 @@
         <v>4.3049469999999985</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -2912,7 +2941,7 @@
         <v>0.56017800000000051</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -2930,7 +2959,7 @@
         <v>3.4717569999999967</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -2948,7 +2977,7 @@
         <v>2.2070239999999899</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -2966,7 +2995,7 @@
         <v>8.7779250000000388</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -2984,7 +3013,7 @@
         <v>13.943848000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -3002,7 +3031,7 @@
         <v>1.3865139999999982</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -3020,7 +3049,7 @@
         <v>3.7634670000000057</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -3034,8 +3063,26 @@
         <v>18.185904000000001</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G69" si="1">E68-B68</f>
+        <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>0.5865860000000005</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>23572.286656000015</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>24164.940385000005</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>592.65372900000034</v>
+      </c>
+      <c r="H70">
+        <f>G70/B70</f>
+        <v>2.5141970214805111E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3045,13 +3092,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B10B9CA-2581-4862-830B-8C8BBBD7F143}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -3062,7 +3109,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3076,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3094,7 +3141,7 @@
         <v>5.9603010000000154</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -3112,7 +3159,7 @@
         <v>40.283635000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3130,7 +3177,7 @@
         <v>7.2084079999999915</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3148,7 +3195,7 @@
         <v>-1.1825060000000036</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3166,7 +3213,7 @@
         <v>5.3873949999999979</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3184,7 +3231,7 @@
         <v>120.2890669999997</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3202,7 +3249,7 @@
         <v>42.783877999999959</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3220,7 +3267,7 @@
         <v>14.945317000005161</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3238,7 +3285,7 @@
         <v>121.60522900000001</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3256,7 +3303,7 @@
         <v>34.7335250000001</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -3274,7 +3321,7 @@
         <v>7.243411999999978</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -3292,7 +3339,7 @@
         <v>21.679569000000015</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3310,7 +3357,7 @@
         <v>24.012699999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -3328,7 +3375,7 @@
         <v>24.066409999999905</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -3346,7 +3393,7 @@
         <v>5.0632969999999773</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -3364,7 +3411,7 @@
         <v>255.99853899999925</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -3382,7 +3429,7 @@
         <v>15.814518000000021</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -3400,7 +3447,7 @@
         <v>5.5390820000000076</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -3418,7 +3465,7 @@
         <v>216.31665399999974</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -3436,7 +3483,7 @@
         <v>37.80212900000015</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -3454,7 +3501,7 @@
         <v>-36.470577000000048</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -3472,7 +3519,7 @@
         <v>49.229313000000047</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -3490,7 +3537,7 @@
         <v>4.5752909999999929</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -3508,7 +3555,7 @@
         <v>10.583988000000033</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -3526,7 +3573,7 @@
         <v>306.28711300000032</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -3544,7 +3591,7 @@
         <v>203.59863600000062</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -3562,7 +3609,7 @@
         <v>61.486699000000044</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -3580,7 +3627,7 @@
         <v>-15.021968000000015</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -3598,7 +3645,7 @@
         <v>30.468936999999983</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -3616,7 +3663,7 @@
         <v>40.730105999999978</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -3634,7 +3681,7 @@
         <v>24.995137</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -3652,7 +3699,7 @@
         <v>271.49805100000049</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -3670,7 +3717,7 @@
         <v>4.003056000000015</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -3688,7 +3735,7 @@
         <v>46.333255999999892</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -3706,7 +3753,7 @@
         <v>2.5838699999999974</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -3724,7 +3771,7 @@
         <v>-38.958980000000338</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -3742,7 +3789,7 @@
         <v>21.314090999999962</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -3760,7 +3807,7 @@
         <v>0.56872999999998797</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3778,7 +3825,7 @@
         <v>17.143742000000032</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -3796,7 +3843,7 @@
         <v>120.64844100000118</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -3814,7 +3861,7 @@
         <v>50.297856000000024</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -3832,7 +3879,7 @@
         <v>-17.785885000000235</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -3850,7 +3897,7 @@
         <v>55.201909000000114</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -3868,7 +3915,7 @@
         <v>42.905642999999827</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -3886,7 +3933,7 @@
         <v>33.077823999999964</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -3904,7 +3951,7 @@
         <v>1.1766149999999982</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -3922,7 +3969,7 @@
         <v>5.0955320000000057</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -3940,7 +3987,7 @@
         <v>109.15405699999997</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -3958,7 +4005,7 @@
         <v>9.297794999999951</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -3976,7 +4023,7 @@
         <v>112.17554100000007</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -3994,7 +4041,7 @@
         <v>10.231204999999989</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -4012,7 +4059,7 @@
         <v>-3.1655240000000049</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -4030,7 +4077,7 @@
         <v>32.91125900000003</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -4048,7 +4095,7 @@
         <v>-35.374750999999833</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -4066,7 +4113,7 @@
         <v>31.127750999999989</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -4084,7 +4131,7 @@
         <v>12.053532000000018</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -4102,7 +4149,7 @@
         <v>34.597660000000133</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -4120,7 +4167,7 @@
         <v>98.123539000000164</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -4138,7 +4185,7 @@
         <v>23.50385</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -4156,7 +4203,7 @@
         <v>422.11670299999969</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -4174,7 +4221,7 @@
         <v>34.344486999999845</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -4192,7 +4239,7 @@
         <v>54.309574999999313</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -4210,7 +4257,7 @@
         <v>26.156253999997716</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -4228,7 +4275,7 @@
         <v>23.762943999999948</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -4246,7 +4293,7 @@
         <v>50.793216999999913</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -4260,8 +4307,26 @@
         <v>344.644993</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G69" si="1">E68-B68</f>
+        <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>12.523349999999994</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>234961.79335100003</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>238321.55278000003</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>3359.7594290000029</v>
+      </c>
+      <c r="H70">
+        <f>G70/B70</f>
+        <v>1.429917341489215E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4271,10 +4336,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D3FF3E-F6F1-480A-99D1-C389F81151FA}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -4285,7 +4350,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4299,7 +4364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4317,7 +4382,7 @@
         <v>52.133792999999969</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -4335,7 +4400,7 @@
         <v>27.937015000000429</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4353,7 +4418,7 @@
         <v>41.323733999999831</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -4371,7 +4436,7 @@
         <v>31.808414000000084</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -4389,7 +4454,7 @@
         <v>36.687197999999967</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -4407,7 +4472,7 @@
         <v>143.63379299999997</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -4425,7 +4490,7 @@
         <v>41.708500000000186</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -4443,7 +4508,7 @@
         <v>1037.7500029999937</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -4461,7 +4526,7 @@
         <v>47.84210500000006</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -4479,7 +4544,7 @@
         <v>138.03515999999991</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -4497,7 +4562,7 @@
         <v>70.26782500000013</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -4515,7 +4580,7 @@
         <v>48.053225999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -4533,7 +4598,7 @@
         <v>33.618167999999969</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -4551,7 +4616,7 @@
         <v>59.037600999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -4569,7 +4634,7 @@
         <v>9.5732450000000426</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -4587,7 +4652,7 @@
         <v>88.987309000000096</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -4605,7 +4670,7 @@
         <v>139.68481799999995</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -4623,7 +4688,7 @@
         <v>23.231143999999972</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -4641,7 +4706,7 @@
         <v>408.14160500000071</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -4659,7 +4724,7 @@
         <v>178.60254299999997</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -4677,7 +4742,7 @@
         <v>125.31982700000026</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -4695,7 +4760,7 @@
         <v>95.643557999999757</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -4713,7 +4778,7 @@
         <v>4.2179979999999944</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -4731,7 +4796,7 @@
         <v>27.531985999999961</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -4749,7 +4814,7 @@
         <v>307.17871399999967</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -4767,7 +4832,7 @@
         <v>245.04687800000102</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -4785,7 +4850,7 @@
         <v>47.754276000000118</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -4803,7 +4868,7 @@
         <v>34.080081000000064</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -4821,7 +4886,7 @@
         <v>70.907962999999654</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -4839,7 +4904,7 @@
         <v>43.013797999999952</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -4857,7 +4922,7 @@
         <v>25.255618999999569</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -4875,7 +4940,7 @@
         <v>-38.154292999999598</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -4893,7 +4958,7 @@
         <v>96.300295999999889</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -4911,7 +4976,7 @@
         <v>64.361574999999903</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -4929,7 +4994,7 @@
         <v>7.8942599999999743</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -4947,7 +5012,7 @@
         <v>586.1875029999992</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -4965,7 +5030,7 @@
         <v>99.743656000000101</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -4983,7 +5048,7 @@
         <v>-0.75475699999992685</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -5001,7 +5066,7 @@
         <v>26.915165000000115</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -5019,7 +5084,7 @@
         <v>116.89892899999995</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -5037,7 +5102,7 @@
         <v>48.21264999999994</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -5055,7 +5120,7 @@
         <v>427.09912499999973</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -5073,7 +5138,7 @@
         <v>102.85132099999964</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -5091,7 +5156,7 @@
         <v>192.72656599999937</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -5109,7 +5174,7 @@
         <v>148.46655599999985</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -5127,7 +5192,7 @@
         <v>-0.76006699999999228</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -5145,7 +5210,7 @@
         <v>4.6050450000000183</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -5163,7 +5228,7 @@
         <v>173.84619499999985</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -5181,7 +5246,7 @@
         <v>161.37317299999995</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -5199,7 +5264,7 @@
         <v>118.46240600000056</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -5217,7 +5282,7 @@
         <v>53.166019000000006</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -5235,7 +5300,7 @@
         <v>-66.870113999999376</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -5253,7 +5318,7 @@
         <v>153.57934900000009</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -5271,7 +5336,7 @@
         <v>55.781985000000077</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -5289,7 +5354,7 @@
         <v>-13.050776999999925</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -5307,7 +5372,7 @@
         <v>70.775638000000072</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -5325,7 +5390,7 @@
         <v>111.5366240000003</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -5343,7 +5408,7 @@
         <v>525.27832400000079</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -5361,7 +5426,7 @@
         <v>109.3916049999998</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -5379,7 +5444,7 @@
         <v>57.117313000000195</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -5397,7 +5462,7 @@
         <v>108.14111599999978</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -5415,7 +5480,7 @@
         <v>46.041994999999588</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -5433,7 +5498,7 @@
         <v>239.9746129999985</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -5451,7 +5516,7 @@
         <v>37.276127000000088</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -5469,7 +5534,7 @@
         <v>211.56347999999889</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -5483,8 +5548,26 @@
         <v>2538.9311560000001</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G69" si="1">E68-B68</f>
+        <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>21.624760000000151</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>426918.35705899994</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>434659.96831700008</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>7741.6112579999935</v>
+      </c>
+      <c r="H70">
+        <f>G70/B70</f>
+        <v>1.8133704325415331E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5494,10 +5577,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03B187FE-E1B4-47D4-AB1D-6743156F5231}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -5508,7 +5591,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5522,7 +5605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5540,7 +5623,7 @@
         <v>6.1273050000000069</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5558,7 +5641,7 @@
         <v>26.633179000000041</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -5576,7 +5659,7 @@
         <v>8.8032379999999932</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -5594,7 +5677,7 @@
         <v>3.0046990000000022</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -5612,7 +5695,7 @@
         <v>3.2119749999999954</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5630,7 +5713,7 @@
         <v>27.992310000000089</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -5648,7 +5731,7 @@
         <v>18.132813000000056</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5666,7 +5749,7 @@
         <v>916.29492199999731</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5684,7 +5767,7 @@
         <v>4.9791950000000043</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5702,7 +5785,7 @@
         <v>28.036499000000049</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -5720,7 +5803,7 @@
         <v>9.4499519999999961</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -5738,7 +5821,7 @@
         <v>10.819351000000012</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -5756,7 +5839,7 @@
         <v>20.860565000000008</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -5774,7 +5857,7 @@
         <v>20.116516000000047</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -5792,7 +5875,7 @@
         <v>3.4865880000000118</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -5810,7 +5893,7 @@
         <v>35.142945000000054</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -5828,7 +5911,7 @@
         <v>19.931548999999961</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -5846,7 +5929,7 @@
         <v>5.7882079999999974</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -5864,7 +5947,7 @@
         <v>111.80090299999983</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -5882,7 +5965,7 @@
         <v>22.991516999999931</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -5900,7 +5983,7 @@
         <v>84.790954000000056</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -5918,7 +6001,7 @@
         <v>61.696777999999995</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -5936,7 +6019,7 @@
         <v>0.70703900000000175</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -5954,7 +6037,7 @@
         <v>6.7722630000000095</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -5972,7 +6055,7 @@
         <v>83.56701599999974</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -5990,7 +6073,7 @@
         <v>46.95666499999993</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -6008,7 +6091,7 @@
         <v>6.7496030000000076</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -6026,7 +6109,7 @@
         <v>7.7737429999999677</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -6044,7 +6127,7 @@
         <v>17.14794900000004</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -6062,7 +6145,7 @@
         <v>27.72909599999997</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -6080,7 +6163,7 @@
         <v>11.201233000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -6098,7 +6181,7 @@
         <v>101.34472599999981</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -6116,7 +6199,7 @@
         <v>14.06320199999999</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -6134,7 +6217,7 @@
         <v>28.536194000000023</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -6152,7 +6235,7 @@
         <v>3.1099090000000018</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -6170,7 +6253,7 @@
         <v>61.580565999999862</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -6188,7 +6271,7 @@
         <v>16.476624000000015</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -6206,7 +6289,7 @@
         <v>2.3186500000000194</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -6224,7 +6307,7 @@
         <v>11.555480999999986</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -6242,7 +6325,7 @@
         <v>25.844849000000067</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -6260,7 +6343,7 @@
         <v>17.720306999999991</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -6278,7 +6361,7 @@
         <v>24.807006999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -6296,7 +6379,7 @@
         <v>23.011169999999993</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -6314,7 +6397,7 @@
         <v>41.03869700000007</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -6332,7 +6415,7 @@
         <v>32.327269999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -6350,7 +6433,7 @@
         <v>1.9154060000000044</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -6368,7 +6451,7 @@
         <v>0.65130700000000274</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -6386,7 +6469,7 @@
         <v>20.604370000000017</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -6404,7 +6487,7 @@
         <v>9.8061220000000162</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -6422,7 +6505,7 @@
         <v>57.565673999999944</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -6440,7 +6523,7 @@
         <v>11.158203000000015</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -6458,7 +6541,7 @@
         <v>40.038819000000331</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -6476,7 +6559,7 @@
         <v>20.416168000000027</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -6494,7 +6577,7 @@
         <v>9.6936040000000503</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -6512,7 +6595,7 @@
         <v>14.827575000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -6530,7 +6613,7 @@
         <v>14.547974000000067</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -6548,7 +6631,7 @@
         <v>40.480712999999923</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -6566,7 +6649,7 @@
         <v>57.893432000000075</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -6584,7 +6667,7 @@
         <v>18.834227999999939</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -6602,7 +6685,7 @@
         <v>12.795867999999984</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -6620,7 +6703,7 @@
         <v>18.539185000000089</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -6638,7 +6721,7 @@
         <v>73.32568399999991</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -6656,7 +6739,7 @@
         <v>81.349121999999625</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -6674,7 +6757,7 @@
         <v>9.2119749999999954</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -6692,7 +6775,7 @@
         <v>71.347168000000011</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -6706,8 +6789,26 @@
         <v>445.87777699999998</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G69" si="1">E68-B68</f>
+        <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>14.689849999999979</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>78888.085628999994</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>81550.209296000015</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>2662.1236669999971</v>
+      </c>
+      <c r="H70">
+        <f>G70/B70</f>
+        <v>3.3745573184772219E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6717,10 +6818,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1CE2D6-43D5-407E-9C7F-4405C5AC1CDD}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -6731,7 +6832,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6745,7 +6846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6763,7 +6864,7 @@
         <v>0.4143449999999973</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -6781,7 +6882,7 @@
         <v>4.7165070000000071</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6799,7 +6900,7 @@
         <v>-5.5555000000001797E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -6817,7 +6918,7 @@
         <v>-0.65029099999999573</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -6835,7 +6936,7 @@
         <v>0.58113900000000029</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6853,7 +6954,7 @@
         <v>0.57424900000000889</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6871,7 +6972,7 @@
         <v>2.0088959999999929</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -6889,7 +6990,7 @@
         <v>69.521483999999873</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6907,7 +7008,7 @@
         <v>0.4037710000000061</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6925,7 +7026,7 @@
         <v>2.6500550000000089</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -6943,7 +7044,7 @@
         <v>-1.6309050000000127</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -6961,7 +7062,7 @@
         <v>1.8706669999999974</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -6979,7 +7080,7 @@
         <v>2.3573379999999986</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -6997,7 +7098,7 @@
         <v>-0.79193099999997685</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -7015,7 +7116,7 @@
         <v>-7.6620999999999384E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -7033,7 +7134,7 @@
         <v>5.1627199999999789</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -7051,7 +7152,7 @@
         <v>0.16216200000000924</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7069,7 +7170,7 @@
         <v>9.8780000000001422E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -7087,7 +7188,7 @@
         <v>15.733216000000084</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -7105,7 +7206,7 @@
         <v>1.9291999999999803</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -7123,7 +7224,7 @@
         <v>-6.5593870000000152</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -7141,7 +7242,7 @@
         <v>9.4483639999999696</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -7159,7 +7260,7 @@
         <v>4.5269999999999921E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -7177,7 +7278,7 @@
         <v>1.2173230000000075</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -7195,7 +7296,7 @@
         <v>17.567138</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -7213,7 +7314,7 @@
         <v>8.3817439999999692</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -7231,7 +7332,7 @@
         <v>-0.65430400000001043</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -7249,7 +7350,7 @@
         <v>0.16104100000001154</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -7267,7 +7368,7 @@
         <v>0.26536600000000021</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -7285,7 +7386,7 @@
         <v>3.3204190000000011</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -7303,7 +7404,7 @@
         <v>0.99281500000000023</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -7321,7 +7422,7 @@
         <v>13.716186999999991</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -7339,7 +7440,7 @@
         <v>0.30914300000000594</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -7357,7 +7458,7 @@
         <v>5.0997319999999888</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -7375,7 +7476,7 @@
         <v>0.28857800000000111</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -7393,7 +7494,7 @@
         <v>2.894012000000032</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -7411,7 +7512,7 @@
         <v>2.9941259999999943</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -7429,7 +7530,7 @@
         <v>-7.1857000000001392E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -7447,7 +7548,7 @@
         <v>1.2476510000000047</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -7465,7 +7566,7 @@
         <v>2.0684819999999604</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -7483,7 +7584,7 @@
         <v>5.7534489999999892</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -7501,7 +7602,7 @@
         <v>-1.5271910000000162</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -7519,7 +7620,7 @@
         <v>1.5707089999999937</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -7537,7 +7638,7 @@
         <v>5.641052000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -7555,7 +7656,7 @@
         <v>4.2797850000000039</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -7573,7 +7674,7 @@
         <v>-1.0457999999999856E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -7591,7 +7692,7 @@
         <v>0.51535900000000368</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -7609,7 +7710,7 @@
         <v>2.6494220000000013</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -7627,7 +7728,7 @@
         <v>-2.2863770000000017</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -7645,7 +7746,7 @@
         <v>-0.49560500000006869</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -7663,7 +7764,7 @@
         <v>1.3677820000000054</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -7681,7 +7782,7 @@
         <v>-0.83807300000000851</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -7699,7 +7800,7 @@
         <v>2.0101549999999975</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -7717,7 +7818,7 @@
         <v>0.2510989999999822</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -7735,7 +7836,7 @@
         <v>2.1098250000000007</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -7753,7 +7854,7 @@
         <v>-0.80651800000001117</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -7771,7 +7872,7 @@
         <v>0.26272599999998647</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -7789,7 +7890,7 @@
         <v>10.962463000000014</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -7807,7 +7908,7 @@
         <v>3.2021640000000104</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -7825,7 +7926,7 @@
         <v>1.1158110000000008</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -7843,7 +7944,7 @@
         <v>3.8548890000000142</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -7861,7 +7962,7 @@
         <v>13.486999999999966</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -7879,7 +7980,7 @@
         <v>13.784668000000011</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -7897,7 +7998,7 @@
         <v>2.6668240000000196</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -7915,7 +8016,7 @@
         <v>6.1494749999999954</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -7931,6 +8032,24 @@
       <c r="G68">
         <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>2.1286769999999962</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>23856.274812</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>24101.784992999997</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>245.5101809999997</v>
+      </c>
+      <c r="H70">
+        <f>G70/B70</f>
+        <v>1.0291220357526443E-2</v>
       </c>
     </row>
   </sheetData>
